--- a/Config/xlsx/Dialogue.xlsx
+++ b/Config/xlsx/Dialogue.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>对话ID</t>
   </si>
@@ -46,6 +46,9 @@
     <t>NextID</t>
   </si>
   <si>
+    <t>图片ID</t>
+  </si>
+  <si>
     <t>小白</t>
   </si>
   <si>
@@ -80,6 +83,12 @@
   </si>
   <si>
     <t>有空我去看看他</t>
+  </si>
+  <si>
+    <t>小黑</t>
+  </si>
+  <si>
+    <t>好</t>
   </si>
 </sst>
 </file>
@@ -1040,15 +1049,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:5">
+    <row r="1" ht="16.5" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1064,108 +1073,152 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>102</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>105</v>
       </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="E9">
+        <v>109</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
